--- a/Result/profitability/3052.xlsx
+++ b/Result/profitability/3052.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.24</v>
+        <v>0.27125</v>
       </c>
       <c r="N2" t="n">
-        <v>13.615</v>
+        <v>12.76125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.215</v>
+        <v>0.245</v>
       </c>
       <c r="N3" t="n">
-        <v>12.5375</v>
+        <v>11.9475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0.255</v>
+        <v>0.27375</v>
       </c>
       <c r="N4" t="n">
-        <v>12.9225</v>
+        <v>12.12125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25875</v>
+        <v>0.28</v>
       </c>
       <c r="N5" t="n">
-        <v>12.72625</v>
+        <v>12.42625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.29375</v>
+        <v>0.31875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.81375</v>
+        <v>13.19625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3475</v>
+        <v>0.39</v>
       </c>
       <c r="N7" t="n">
-        <v>14.645</v>
+        <v>14.75125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>0.43375</v>
+        <v>0.47125</v>
       </c>
       <c r="N8" t="n">
-        <v>17.21875</v>
+        <v>17.18875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0.585</v>
+        <v>0.5850000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>23.4</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3052</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D75" t="n">
+        <v>940</v>
+      </c>
+      <c r="E75" t="n">
+        <v>98</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>101</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.55625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02471678681771372</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2021903959561919</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
